--- a/paper/source_data/ed2_source_data.xlsx
+++ b/paper/source_data/ed2_source_data.xlsx
@@ -496,12 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>**Extended Data Fig. 2 | Participant flow and cohort characteristics.**
-**a**, AI-READI. The 1,928 development adults are reused throughout and scored out of fold. The 352-person official test was scored once by the predecessor model in August 2026, whose paired primary end point was not met, and once by BRAN on 5 October 2026 as a previously accessed check (Extended Data Fig. 1).
-**b**, Development beside the whole local release, which also holds the official test. Study group is held only for the release, age has no summary aggregate, and sex, race and ethnicity need controlled access, so these cells are PLACEHOLDER. The encoder has no sex, race, ethnicity or medication input. UAB, University of Alabama at Birmingham. UCSD, University of California San Diego. UW, University of Washington.
-**c**, Prevalence of 26 self-reported conditions among development adults with an explicit answer, with floored counts of yes and of answers. Each condition had at least 50 people with and 50 without it before any model was scored. MCI, mild cognitive impairment.
-**d**, External cohorts, one row per analysis, with the figure showing it. Encoder says whether a cohort trained the encoder (training source, people in the final fit) or never did (unseen), and scored before marks cohorts an earlier BRAN checkpoint had also scored. No external cohort has retinal photographs, so every external row tests the clinical-only route. The MIMIC-IV replication rule was not met, eICU had insufficient support, and the MIMIC-III CareVue and HiRID counts are PLACEHOLDER. ED, Extended Data.
-Counts with ≥ are lower bounds rounded down to 20, KNHANES survey counts are rounded down to 10, and other counts are exact.</t>
+          <t>**Extended Data Fig. 2 | Participant flow and cohort characteristics.** **a**, AI-READI. The 1,928 development adults are reused throughout and scored out of fold. The 352-person official test was scored once by the predecessor model (August 2026, paired primary end point not met) and once by BRAN (5 October 2026, a previously accessed check, Extended Data Fig. 1). **b**, Development beside the whole local release, which includes the official test. Study group is held only for the release, age has no summary aggregate and sex, race and ethnicity need controlled access, so these cells are PLACEHOLDER. The encoder has no sex, race, ethnicity or medication input. UAB, UCSD and UW, University of Alabama at Birmingham, University of California San Diego and University of Washington. **c**, Prevalence of 26 self-reported conditions among development adults with an explicit answer, with floored counts of yes and of answers. Each condition had at least 50 people with and 50 without it before any model was scored. MCI, mild cognitive impairment. **d**, External cohorts (Extended Data Table 1), one row per analysis, with the figure showing it. Encoder gives training-source exposure (people in the final fit) or unseen, and scored before marks cohorts an earlier checkpoint also scored. With no retinal photographs, every external row tests the clinical-only route. The MIMIC-IV replication rule was not met, eICU had insufficient support, and MIMIC-III CareVue and HiRID counts are PLACEHOLDER. ED, Extended Data. Counts with ≥ are floored to 20 (KNHANES survey counts to 10), and others are exact.</t>
         </is>
       </c>
     </row>
@@ -734,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -743,6 +738,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -752,68 +748,48 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>count_type gives the kind of count in each row (disclosure review of 6 October 2026, b). Site, image, device and study-group counts are exact counts of the local AI-READI release and its development subset, and people with colour fundus photographs are lower bounds rounded down to 20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>characteristic</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>development</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>local_release</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>count_type</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>source_sha256</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>UAB</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>686 (35.6%)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>800 (35.1%)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>PATIENT_ATLAS_V5_CROSSMODAL_UTILITY_ATTEMPT2.json</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>94e46967f1b12a2dc2d669791162dab80531e79bff6a5410826084d8663184d3</t>
         </is>
       </c>
     </row>
@@ -825,25 +801,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UCSD</t>
+          <t>UAB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>578 (30.0%)</t>
+          <t>686 (35.6%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>682 (29.9%)</t>
+          <t>800 (35.1%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>PATIENT_ATLAS_V5_CROSSMODAL_UTILITY_ATTEMPT2.json</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>94e46967f1b12a2dc2d669791162dab80531e79bff6a5410826084d8663184d3</t>
         </is>
@@ -857,25 +838,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UW</t>
+          <t>UCSD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>664 (34.4%)</t>
+          <t>578 (30.0%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>798 (35.0%)</t>
+          <t>682 (29.9%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>PATIENT_ATLAS_V5_CROSSMODAL_UTILITY_ATTEMPT2.json</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>94e46967f1b12a2dc2d669791162dab80531e79bff6a5410826084d8663184d3</t>
         </is>
@@ -884,30 +870,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colour fundus photographs</t>
+          <t>Site</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>UW</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>≥1,920</t>
+          <t>664 (34.4%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>≥2,260</t>
+          <t>798 (35.0%)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>PATIENT_ATLAS_V5_CROSSMODAL_UTILITY_ATTEMPT2.json</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>94e46967f1b12a2dc2d669791162dab80531e79bff6a5410826084d8663184d3</t>
         </is>
@@ -921,27 +912,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>People</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>42,558</t>
+          <t>≥1,920</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>50,315</t>
+          <t>≥2,260</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PATIENT_ATLAS_RAW_SOURCE_AUDIT.json</t>
+          <t>lower bound rounded down to 20</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>107b5d619b41612887707c7b6948ec0fa53cab76013745d21d061cfe45fb9a2f</t>
+          <t>PATIENT_ATLAS_V5_CROSSMODAL_UTILITY_ATTEMPT2.json</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>94e46967f1b12a2dc2d669791162dab80531e79bff6a5410826084d8663184d3</t>
         </is>
       </c>
     </row>
@@ -953,27 +949,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eidon (iCare), images</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15,234 (35.8%)</t>
+          <t>42,558</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Not counted</t>
+          <t>50,315</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PATIENT_ATLAS_EXPLORATORY_COHORT_SUMMARY.json</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>f4aa23f7bf790a8913bb6ac0e54cfe03b95e27cf4cbe58f6ac6a9cdf30c7f308</t>
+          <t>PATIENT_ATLAS_RAW_SOURCE_AUDIT.json</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>107b5d619b41612887707c7b6948ec0fa53cab76013745d21d061cfe45fb9a2f</t>
         </is>
       </c>
     </row>
@@ -985,12 +986,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aurora (Optomed), images</t>
+          <t>Eidon (iCare), images</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8,275 (19.4%)</t>
+          <t>15,234 (35.8%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1000,10 +1001,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>PATIENT_ATLAS_EXPLORATORY_COHORT_SUMMARY.json</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>f4aa23f7bf790a8913bb6ac0e54cfe03b95e27cf4cbe58f6ac6a9cdf30c7f308</t>
         </is>
@@ -1017,12 +1023,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Maestro2 (Topcon), images</t>
+          <t>Aurora (Optomed), images</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7,687 (18.1%)</t>
+          <t>8,275 (19.4%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1032,10 +1038,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>PATIENT_ATLAS_EXPLORATORY_COHORT_SUMMARY.json</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>f4aa23f7bf790a8913bb6ac0e54cfe03b95e27cf4cbe58f6ac6a9cdf30c7f308</t>
         </is>
@@ -1049,12 +1060,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Triton (Topcon), images</t>
+          <t>Maestro2 (Topcon), images</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11,362 (26.7%)</t>
+          <t>7,687 (18.1%)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1064,10 +1075,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>PATIENT_ATLAS_EXPLORATORY_COHORT_SUMMARY.json</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>f4aa23f7bf790a8913bb6ac0e54cfe03b95e27cf4cbe58f6ac6a9cdf30c7f308</t>
         </is>
@@ -1076,32 +1092,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Study group</t>
+          <t>Colour fundus photographs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Healthy</t>
+          <t>Triton (Topcon), images</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PLACEHOLDER</t>
+          <t>11,362 (26.7%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>776 (34.0%)</t>
+          <t>Not counted</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PATIENT_ATLAS_RAW_SOURCE_AUDIT.json</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>107b5d619b41612887707c7b6948ec0fa53cab76013745d21d061cfe45fb9a2f</t>
+          <t>PATIENT_ATLAS_EXPLORATORY_COHORT_SUMMARY.json</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>f4aa23f7bf790a8913bb6ac0e54cfe03b95e27cf4cbe58f6ac6a9cdf30c7f308</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1134,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prediabetes, lifestyle controlled</t>
+          <t>Healthy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1123,15 +1144,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>560 (24.6%)</t>
+          <t>776 (34.0%)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>PATIENT_ATLAS_RAW_SOURCE_AUDIT.json</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>107b5d619b41612887707c7b6948ec0fa53cab76013745d21d061cfe45fb9a2f</t>
         </is>
@@ -1145,7 +1171,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Oral or non-insulin medication</t>
+          <t>Prediabetes, lifestyle controlled</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1155,15 +1181,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>686 (30.1%)</t>
+          <t>560 (24.6%)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>PATIENT_ATLAS_RAW_SOURCE_AUDIT.json</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>107b5d619b41612887707c7b6948ec0fa53cab76013745d21d061cfe45fb9a2f</t>
         </is>
@@ -1177,7 +1208,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Insulin dependent</t>
+          <t>Oral or non-insulin medication</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1187,15 +1218,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>258 (11.3%)</t>
+          <t>686 (30.1%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>PATIENT_ATLAS_RAW_SOURCE_AUDIT.json</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>107b5d619b41612887707c7b6948ec0fa53cab76013745d21d061cfe45fb9a2f</t>
         </is>
@@ -1204,12 +1240,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>No summary aggregate</t>
+          <t>Study group</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Insulin dependent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1219,47 +1255,94 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PLACEHOLDER</t>
+          <t>258 (11.3%)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PATIENT_ATLAS_V5_CROSSMODAL_UTILITY_ATTEMPT2.json</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>94e46967f1b12a2dc2d669791162dab80531e79bff6a5410826084d8663184d3</t>
+          <t>PATIENT_ATLAS_RAW_SOURCE_AUDIT.json</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>107b5d619b41612887707c7b6948ec0fa53cab76013745d21d061cfe45fb9a2f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>No summary aggregate</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>no count, PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PATIENT_ATLAS_V5_CROSSMODAL_UTILITY_ATTEMPT2.json</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>94e46967f1b12a2dc2d669791162dab80531e79bff6a5410826084d8663184d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Not held in the record</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Sex, race and ethnicity</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>PLACEHOLDER</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>PLACEHOLDER</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no count, PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>BRAN_MASTER_OUTLINE_2026-09-30_rev2.md</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>ba33ff74e491f09fd4d3c0d1ff18500916d4c134a4f1dd6a373a7faeb5aa0e88</t>
         </is>
